--- a/dataset_2022/benchmark_stable.xlsx
+++ b/dataset_2022/benchmark_stable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IoT\4-Elevate\GPT4_vitas\dataset_2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464351B8-742A-41CF-917D-B6A03BE98B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFAA09A-A3A1-4893-B490-BFA041CFF878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="640" yWindow="960" windowWidth="13280" windowHeight="11220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>all_ages</t>
   </si>
   <si>
-    <t>B08DF6XZSF</t>
-  </si>
-  <si>
     <t>Me</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
   </si>
   <si>
     <t>Business &amp; Finance</t>
-  </si>
-  <si>
-    <t>B094NPPJ24</t>
   </si>
   <si>
     <t>Zyrtec</t>
@@ -158,9 +152,6 @@
   </si>
   <si>
     <t>Lifestyle</t>
-  </si>
-  <si>
-    <t>B07MK35XBS</t>
   </si>
   <si>
     <t>ZauberBot</t>
@@ -2595,6 +2586,18 @@
   </si>
   <si>
     <t>Build a PC Sales</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B08DF6XZSF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B094NPPJ24</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B07MK35XBS</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3107,34 +3110,34 @@
     </row>
     <row r="2" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="J2" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>2</v>
@@ -3143,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>3</v>
@@ -3152,39 +3155,39 @@
         <v>4</v>
       </c>
       <c r="P2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="V2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="D3" s="7">
         <v>1.9</v>
@@ -3199,226 +3202,226 @@
         <v>1</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="V3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" s="7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="J4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="L4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="O4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P4" s="8" t="s">
+      <c r="S4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="T4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="U4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="V4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W4" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W4" s="7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="J5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="L5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="O5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="R5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="P5" s="8" t="s">
+      <c r="S5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q5" s="7" t="s">
+      <c r="T5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="U5" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="V5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>534</v>
+      </c>
+      <c r="I6" t="s">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
+      <c r="J6" t="s">
         <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>537</v>
-      </c>
-      <c r="I6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" t="s">
-        <v>78</v>
       </c>
       <c r="K6" t="s">
         <v>2</v>
@@ -3427,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N6" t="s">
         <v>3</v>
@@ -3436,110 +3439,110 @@
         <v>4</v>
       </c>
       <c r="P6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" t="s">
+        <v>79</v>
+      </c>
+      <c r="S6" t="s">
         <v>80</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="T6" t="s">
         <v>81</v>
       </c>
-      <c r="R6" t="s">
+      <c r="U6" t="s">
         <v>82</v>
-      </c>
-      <c r="S6" t="s">
-        <v>83</v>
-      </c>
-      <c r="T6" t="s">
-        <v>84</v>
-      </c>
-      <c r="U6" t="s">
-        <v>85</v>
       </c>
       <c r="V6" t="s">
         <v>5</v>
       </c>
       <c r="W6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="I7" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="J7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="N7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="O7" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M7" s="7" t="s">
+      <c r="P7" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="Q7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="R7" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="S7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="Q7" s="7" t="s">
+      <c r="T7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="U7" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="V7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W7" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W7" s="7" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D8" s="7">
         <v>5</v>
@@ -3554,13 +3557,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>2</v>
@@ -3569,48 +3572,48 @@
         <v>1</v>
       </c>
       <c r="M8" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="Q8" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="R8" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="S8" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Q8" s="7" t="s">
+      <c r="T8" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="U8" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="S8" s="7" t="s">
+      <c r="V8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W8" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D9" s="5">
         <v>3.4</v>
@@ -3625,13 +3628,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>2</v>
@@ -3640,48 +3643,48 @@
         <v>1</v>
       </c>
       <c r="M9" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="5" t="s">
+      <c r="S9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="5" t="s">
+      <c r="T9" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="R9" s="5" t="s">
+      <c r="U9" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="S9" s="5" t="s">
+      <c r="V9" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="T9" s="5" t="s">
+      <c r="W9" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="W9" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D10" s="7">
         <v>4</v>
@@ -3696,205 +3699,205 @@
         <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K10" s="7" t="s">
+      <c r="N10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="P10" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="R10" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="S10" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="T10" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="U10" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="S10" s="7" t="s">
+      <c r="V10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W10" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="V10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="J11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="L11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="N11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P11" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="5" t="s">
+      <c r="Q11" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M11" s="5" t="s">
+      <c r="R11" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="N11" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P11" s="6" t="s">
+      <c r="S11" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="Q11" s="5" t="s">
+      <c r="T11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="R11" s="5" t="s">
+      <c r="U11" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="V11" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="J12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="N12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="Q12" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="s">
+      <c r="R12" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="N12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="8" t="s">
+      <c r="S12" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="Q12" s="7" t="s">
+      <c r="T12" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="U12" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="T12" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="U12" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="V12" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:23" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
@@ -3909,84 +3912,84 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="N13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P13" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="Q13" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="7" t="s">
+      <c r="R13" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="N13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P13" s="7" t="s">
+      <c r="S13" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="Q13" s="7" t="s">
+      <c r="T13" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="R13" s="7" t="s">
+      <c r="U13" s="7" t="s">
         <v>187</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="U13" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="V13" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="J14" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>2</v>
@@ -3995,48 +3998,48 @@
         <v>1</v>
       </c>
       <c r="M14" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="R14" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="N14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="6" t="s">
+      <c r="S14" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="Q14" s="5" t="s">
+      <c r="T14" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="R14" s="5" t="s">
+      <c r="U14" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="T14" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="U14" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="V14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W14" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D15" s="5">
         <v>5</v>
@@ -4051,63 +4054,63 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="Q15" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="5" t="s">
+      <c r="R15" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="6" t="s">
+      <c r="S15" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="Q15" s="5" t="s">
+      <c r="T15" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="R15" s="5" t="s">
+      <c r="U15" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="T15" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="V15" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W15" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D16" s="5">
         <v>5</v>
@@ -4122,13 +4125,13 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>2</v>
@@ -4137,48 +4140,48 @@
         <v>1</v>
       </c>
       <c r="M16" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="R16" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="O16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P16" s="5" t="s">
+      <c r="S16" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="Q16" s="5" t="s">
+      <c r="T16" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="R16" s="5" t="s">
+      <c r="U16" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="S16" s="5" t="s">
+      <c r="V16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="W16" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="T16" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="W16" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D17" s="5">
         <v>5</v>
@@ -4193,13 +4196,13 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>2</v>
@@ -4208,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>3</v>
@@ -4217,110 +4220,110 @@
         <v>4</v>
       </c>
       <c r="P17" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="S17" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="Q17" s="5" t="s">
+      <c r="T17" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="R17" s="5" t="s">
+      <c r="U17" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="V17" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W17" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="J18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D18" s="5">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="N18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="Q18" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M18" s="5" t="s">
+      <c r="R18" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="N18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="6" t="s">
+      <c r="S18" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="Q18" s="5" t="s">
+      <c r="T18" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="R18" s="5" t="s">
+      <c r="U18" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="V18" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W18" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D19" s="5">
         <v>2.6</v>
@@ -4335,63 +4338,63 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="P19" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="Q19" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="M19" s="5" t="s">
+      <c r="R19" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="N19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P19" s="6" t="s">
+      <c r="S19" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="Q19" s="5" t="s">
+      <c r="T19" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="R19" s="5" t="s">
+      <c r="U19" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="T19" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>269</v>
       </c>
       <c r="V19" s="5" t="s">
         <v>5</v>
       </c>
       <c r="W19" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B20" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -4406,13 +4409,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I20" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="J20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K20" t="s">
         <v>2</v>
@@ -4421,48 +4424,48 @@
         <v>1</v>
       </c>
       <c r="M20" t="s">
+        <v>272</v>
+      </c>
+      <c r="N20" t="s">
+        <v>273</v>
+      </c>
+      <c r="O20" t="s">
+        <v>273</v>
+      </c>
+      <c r="P20" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q20" t="s">
         <v>275</v>
       </c>
-      <c r="N20" t="s">
+      <c r="R20" t="s">
+        <v>274</v>
+      </c>
+      <c r="S20" t="s">
         <v>276</v>
       </c>
-      <c r="O20" t="s">
-        <v>276</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="T20" t="s">
         <v>277</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="U20" t="s">
         <v>278</v>
       </c>
-      <c r="R20" t="s">
-        <v>277</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="V20" t="s">
+        <v>33</v>
+      </c>
+      <c r="W20" t="s">
         <v>279</v>
-      </c>
-      <c r="T20" t="s">
-        <v>280</v>
-      </c>
-      <c r="U20" t="s">
-        <v>281</v>
-      </c>
-      <c r="V20" t="s">
-        <v>35</v>
-      </c>
-      <c r="W20" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C21" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D21">
         <v>2.2999999999999998</v>
@@ -4477,46 +4480,46 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
+        <v>283</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J21" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>285</v>
+      </c>
+      <c r="N21" t="s">
         <v>286</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="O21" t="s">
         <v>287</v>
       </c>
-      <c r="J21" t="s">
-        <v>10</v>
-      </c>
-      <c r="K21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" t="s">
-        <v>1</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="P21" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="N21" t="s">
+      <c r="Q21" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" t="s">
         <v>289</v>
       </c>
-      <c r="O21" t="s">
+      <c r="T21" t="s">
         <v>290</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="U21" t="s">
         <v>291</v>
       </c>
-      <c r="Q21" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" t="s">
-        <v>292</v>
-      </c>
-      <c r="T21" t="s">
-        <v>293</v>
-      </c>
-      <c r="U21" t="s">
-        <v>294</v>
-      </c>
       <c r="V21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W21" t="s">
         <v>3</v>
@@ -4524,13 +4527,13 @@
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D22">
         <v>3.4</v>
@@ -4545,63 +4548,63 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
+        <v>294</v>
+      </c>
+      <c r="I22" t="s">
+        <v>295</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" t="s">
+        <v>296</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M22" t="s">
         <v>297</v>
       </c>
-      <c r="I22" t="s">
+      <c r="N22" t="s">
         <v>298</v>
       </c>
-      <c r="J22" t="s">
-        <v>73</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="O22" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="L22" t="s">
-        <v>1</v>
-      </c>
-      <c r="M22" t="s">
+      <c r="Q22" t="s">
         <v>300</v>
       </c>
-      <c r="N22" t="s">
+      <c r="R22" t="s">
         <v>301</v>
       </c>
-      <c r="O22" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="2" t="s">
+      <c r="S22" t="s">
         <v>302</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="T22" t="s">
         <v>303</v>
       </c>
-      <c r="R22" t="s">
+      <c r="U22" t="s">
         <v>304</v>
-      </c>
-      <c r="S22" t="s">
-        <v>305</v>
-      </c>
-      <c r="T22" t="s">
-        <v>306</v>
-      </c>
-      <c r="U22" t="s">
-        <v>307</v>
       </c>
       <c r="V22" t="s">
         <v>5</v>
       </c>
       <c r="W22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C23" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D23">
         <v>4.0999999999999996</v>
@@ -4616,46 +4619,46 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
+        <v>309</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" t="s">
+        <v>311</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1</v>
+      </c>
+      <c r="M23" t="s">
         <v>312</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="N23" t="s">
         <v>313</v>
       </c>
-      <c r="J23" t="s">
-        <v>39</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="O23" t="s">
         <v>314</v>
       </c>
-      <c r="L23" t="s">
-        <v>1</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="P23" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="N23" t="s">
+      <c r="Q23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" t="s">
         <v>316</v>
       </c>
-      <c r="O23" t="s">
+      <c r="T23" t="s">
         <v>317</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="U23" t="s">
         <v>318</v>
       </c>
-      <c r="Q23" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" t="s">
-        <v>319</v>
-      </c>
-      <c r="T23" t="s">
-        <v>320</v>
-      </c>
-      <c r="U23" t="s">
-        <v>321</v>
-      </c>
       <c r="V23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W23" t="s">
         <v>3</v>
@@ -4663,13 +4666,13 @@
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B24" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C24" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D24">
         <v>2.7</v>
@@ -4684,63 +4687,63 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
+        <v>322</v>
+      </c>
+      <c r="I24" t="s">
+        <v>323</v>
+      </c>
+      <c r="J24" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1</v>
+      </c>
+      <c r="M24" t="s">
+        <v>324</v>
+      </c>
+      <c r="N24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="I24" t="s">
+      <c r="Q24" t="s">
         <v>326</v>
       </c>
-      <c r="J24" t="s">
-        <v>87</v>
-      </c>
-      <c r="K24" t="s">
-        <v>61</v>
-      </c>
-      <c r="L24" t="s">
-        <v>1</v>
-      </c>
-      <c r="M24" t="s">
+      <c r="R24" t="s">
         <v>327</v>
       </c>
-      <c r="N24" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="2" t="s">
+      <c r="S24" t="s">
         <v>328</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="T24" t="s">
         <v>329</v>
       </c>
-      <c r="R24" t="s">
+      <c r="U24" t="s">
         <v>330</v>
-      </c>
-      <c r="S24" t="s">
-        <v>331</v>
-      </c>
-      <c r="T24" t="s">
-        <v>332</v>
-      </c>
-      <c r="U24" t="s">
-        <v>333</v>
       </c>
       <c r="V24" t="s">
         <v>5</v>
       </c>
       <c r="W24" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B25" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C25" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D25">
         <v>2.8</v>
@@ -4755,63 +4758,63 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
+        <v>335</v>
+      </c>
+      <c r="I25" t="s">
+        <v>336</v>
+      </c>
+      <c r="J25" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>337</v>
+      </c>
+      <c r="N25" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" t="s">
+        <v>3</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="I25" t="s">
+      <c r="Q25" t="s">
         <v>339</v>
       </c>
-      <c r="J25" t="s">
-        <v>73</v>
-      </c>
-      <c r="K25" t="s">
-        <v>61</v>
-      </c>
-      <c r="L25" t="s">
-        <v>1</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="R25" t="s">
         <v>340</v>
       </c>
-      <c r="N25" t="s">
-        <v>3</v>
-      </c>
-      <c r="O25" t="s">
-        <v>3</v>
-      </c>
-      <c r="P25" s="2" t="s">
+      <c r="S25" t="s">
         <v>341</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="T25" t="s">
         <v>342</v>
       </c>
-      <c r="R25" t="s">
+      <c r="U25" t="s">
         <v>343</v>
-      </c>
-      <c r="S25" t="s">
-        <v>344</v>
-      </c>
-      <c r="T25" t="s">
-        <v>345</v>
-      </c>
-      <c r="U25" t="s">
-        <v>346</v>
       </c>
       <c r="V25" t="s">
         <v>5</v>
       </c>
       <c r="W25" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B26" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C26" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D26">
         <v>1.2</v>
@@ -4826,63 +4829,63 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
+        <v>348</v>
+      </c>
+      <c r="I26" t="s">
+        <v>349</v>
+      </c>
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" t="s">
+        <v>350</v>
+      </c>
+      <c r="L26" t="s">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
         <v>351</v>
       </c>
-      <c r="I26" t="s">
+      <c r="N26" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" t="s">
         <v>352</v>
       </c>
-      <c r="J26" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="Q26" t="s">
         <v>353</v>
       </c>
-      <c r="L26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="R26" t="s">
         <v>354</v>
       </c>
-      <c r="N26" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="S26" t="s">
         <v>355</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="T26" t="s">
         <v>356</v>
       </c>
-      <c r="R26" t="s">
+      <c r="U26" t="s">
         <v>357</v>
-      </c>
-      <c r="S26" t="s">
-        <v>358</v>
-      </c>
-      <c r="T26" t="s">
-        <v>359</v>
-      </c>
-      <c r="U26" t="s">
-        <v>360</v>
       </c>
       <c r="V26" t="s">
         <v>5</v>
       </c>
       <c r="W26" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B27" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C27" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D27">
         <v>4.5</v>
@@ -4897,63 +4900,63 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
+        <v>362</v>
+      </c>
+      <c r="I27" t="s">
+        <v>363</v>
+      </c>
+      <c r="J27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" t="s">
+        <v>1</v>
+      </c>
+      <c r="M27" t="s">
+        <v>364</v>
+      </c>
+      <c r="N27" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" t="s">
         <v>365</v>
       </c>
-      <c r="I27" t="s">
+      <c r="Q27" t="s">
         <v>366</v>
       </c>
-      <c r="J27" t="s">
-        <v>10</v>
-      </c>
-      <c r="K27" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" t="s">
-        <v>1</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="R27" t="s">
         <v>367</v>
       </c>
-      <c r="N27" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="S27" t="s">
         <v>368</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="T27" t="s">
         <v>369</v>
       </c>
-      <c r="R27" t="s">
+      <c r="U27" t="s">
         <v>370</v>
-      </c>
-      <c r="S27" t="s">
-        <v>371</v>
-      </c>
-      <c r="T27" t="s">
-        <v>372</v>
-      </c>
-      <c r="U27" t="s">
-        <v>373</v>
       </c>
       <c r="V27" t="s">
         <v>5</v>
       </c>
       <c r="W27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B28" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C28" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D28">
         <v>3.6</v>
@@ -4968,63 +4971,63 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
+        <v>375</v>
+      </c>
+      <c r="I28" t="s">
+        <v>376</v>
+      </c>
+      <c r="J28" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>377</v>
+      </c>
+      <c r="N28" t="s">
+        <v>3</v>
+      </c>
+      <c r="O28" t="s">
+        <v>3</v>
+      </c>
+      <c r="P28" t="s">
         <v>378</v>
       </c>
-      <c r="I28" t="s">
+      <c r="Q28" t="s">
         <v>379</v>
       </c>
-      <c r="J28" t="s">
-        <v>183</v>
-      </c>
-      <c r="K28" t="s">
-        <v>61</v>
-      </c>
-      <c r="L28" t="s">
-        <v>1</v>
-      </c>
-      <c r="M28" t="s">
+      <c r="R28" t="s">
         <v>380</v>
       </c>
-      <c r="N28" t="s">
-        <v>3</v>
-      </c>
-      <c r="O28" t="s">
-        <v>3</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="S28" t="s">
         <v>381</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="T28" t="s">
         <v>382</v>
       </c>
-      <c r="R28" t="s">
+      <c r="U28" t="s">
         <v>383</v>
-      </c>
-      <c r="S28" t="s">
-        <v>384</v>
-      </c>
-      <c r="T28" t="s">
-        <v>385</v>
-      </c>
-      <c r="U28" t="s">
-        <v>386</v>
       </c>
       <c r="V28" t="s">
         <v>5</v>
       </c>
       <c r="W28" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B29" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C29" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D29">
         <v>2.7</v>
@@ -5039,84 +5042,84 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
+        <v>388</v>
+      </c>
+      <c r="I29" t="s">
+        <v>389</v>
+      </c>
+      <c r="J29" t="s">
+        <v>180</v>
+      </c>
+      <c r="K29" t="s">
+        <v>153</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>390</v>
+      </c>
+      <c r="N29" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" t="s">
         <v>391</v>
       </c>
-      <c r="I29" t="s">
+      <c r="Q29" t="s">
         <v>392</v>
       </c>
-      <c r="J29" t="s">
-        <v>183</v>
-      </c>
-      <c r="K29" t="s">
-        <v>156</v>
-      </c>
-      <c r="L29" t="s">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
+      <c r="R29" t="s">
         <v>393</v>
       </c>
-      <c r="N29" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="S29" t="s">
         <v>394</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="T29" t="s">
         <v>395</v>
       </c>
-      <c r="R29" t="s">
+      <c r="U29" t="s">
         <v>396</v>
-      </c>
-      <c r="S29" t="s">
-        <v>397</v>
-      </c>
-      <c r="T29" t="s">
-        <v>398</v>
-      </c>
-      <c r="U29" t="s">
-        <v>399</v>
       </c>
       <c r="V29" t="s">
         <v>5</v>
       </c>
       <c r="W29" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>398</v>
+      </c>
+      <c r="B30" t="s">
+        <v>399</v>
+      </c>
+      <c r="C30" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>400</v>
+      </c>
+      <c r="I30" t="s">
         <v>401</v>
       </c>
-      <c r="B30" t="s">
-        <v>402</v>
-      </c>
-      <c r="C30" t="s">
-        <v>194</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>403</v>
-      </c>
-      <c r="I30" t="s">
-        <v>404</v>
-      </c>
       <c r="J30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K30" t="s">
         <v>2</v>
@@ -5125,48 +5128,48 @@
         <v>1</v>
       </c>
       <c r="M30" t="s">
+        <v>402</v>
+      </c>
+      <c r="N30" t="s">
+        <v>3</v>
+      </c>
+      <c r="O30" t="s">
+        <v>3</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>404</v>
+      </c>
+      <c r="R30" t="s">
         <v>405</v>
       </c>
-      <c r="N30" t="s">
-        <v>3</v>
-      </c>
-      <c r="O30" t="s">
-        <v>3</v>
-      </c>
-      <c r="P30" s="2" t="s">
+      <c r="S30" t="s">
         <v>406</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="T30" t="s">
         <v>407</v>
       </c>
-      <c r="R30" t="s">
+      <c r="U30" t="s">
         <v>408</v>
       </c>
-      <c r="S30" t="s">
-        <v>409</v>
-      </c>
-      <c r="T30" t="s">
-        <v>410</v>
-      </c>
-      <c r="U30" t="s">
-        <v>411</v>
-      </c>
       <c r="V30" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="W30" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B31" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C31" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -5181,13 +5184,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I31" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K31" t="s">
         <v>2</v>
@@ -5196,48 +5199,48 @@
         <v>1</v>
       </c>
       <c r="M31" t="s">
+        <v>414</v>
+      </c>
+      <c r="N31" t="s">
+        <v>3</v>
+      </c>
+      <c r="O31" t="s">
+        <v>3</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>416</v>
+      </c>
+      <c r="R31" t="s">
         <v>417</v>
       </c>
-      <c r="N31" t="s">
-        <v>3</v>
-      </c>
-      <c r="O31" t="s">
-        <v>3</v>
-      </c>
-      <c r="P31" s="2" t="s">
+      <c r="S31" t="s">
         <v>418</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="T31" t="s">
         <v>419</v>
       </c>
-      <c r="R31" t="s">
+      <c r="U31" t="s">
         <v>420</v>
-      </c>
-      <c r="S31" t="s">
-        <v>421</v>
-      </c>
-      <c r="T31" t="s">
-        <v>422</v>
-      </c>
-      <c r="U31" t="s">
-        <v>423</v>
       </c>
       <c r="V31" t="s">
         <v>5</v>
       </c>
       <c r="W31" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B32" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C32" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -5252,13 +5255,13 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="I32" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J32" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K32" t="s">
         <v>2</v>
@@ -5267,48 +5270,48 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
+        <v>427</v>
+      </c>
+      <c r="N32" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>429</v>
+      </c>
+      <c r="R32" t="s">
         <v>430</v>
       </c>
-      <c r="N32" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="S32" t="s">
         <v>431</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="T32" t="s">
         <v>432</v>
       </c>
-      <c r="R32" t="s">
+      <c r="U32" t="s">
         <v>433</v>
       </c>
-      <c r="S32" t="s">
+      <c r="V32" t="s">
+        <v>128</v>
+      </c>
+      <c r="W32" t="s">
         <v>434</v>
-      </c>
-      <c r="T32" t="s">
-        <v>435</v>
-      </c>
-      <c r="U32" t="s">
-        <v>436</v>
-      </c>
-      <c r="V32" t="s">
-        <v>131</v>
-      </c>
-      <c r="W32" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B33" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C33" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D33">
         <v>3.3</v>
@@ -5323,63 +5326,63 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
+        <v>494</v>
+      </c>
+      <c r="I33" t="s">
+        <v>438</v>
+      </c>
+      <c r="J33" t="s">
+        <v>84</v>
+      </c>
+      <c r="K33" t="s">
         <v>497</v>
       </c>
-      <c r="I33" t="s">
+      <c r="L33" t="s">
+        <v>1</v>
+      </c>
+      <c r="M33" t="s">
+        <v>498</v>
+      </c>
+      <c r="N33" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>440</v>
+      </c>
+      <c r="R33" t="s">
         <v>441</v>
       </c>
-      <c r="J33" t="s">
-        <v>87</v>
-      </c>
-      <c r="K33" t="s">
-        <v>500</v>
-      </c>
-      <c r="L33" t="s">
-        <v>1</v>
-      </c>
-      <c r="M33" t="s">
-        <v>501</v>
-      </c>
-      <c r="N33" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="2" t="s">
+      <c r="S33" t="s">
         <v>442</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="T33" t="s">
         <v>443</v>
       </c>
-      <c r="R33" t="s">
+      <c r="U33" t="s">
         <v>444</v>
-      </c>
-      <c r="S33" t="s">
-        <v>445</v>
-      </c>
-      <c r="T33" t="s">
-        <v>446</v>
-      </c>
-      <c r="U33" t="s">
-        <v>447</v>
       </c>
       <c r="V33" t="s">
         <v>5</v>
       </c>
       <c r="W33" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B34" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C34" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -5394,23 +5397,23 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="I34" t="s">
+        <v>496</v>
+      </c>
+      <c r="J34" t="s">
+        <v>36</v>
+      </c>
+      <c r="K34" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1</v>
+      </c>
+      <c r="M34" t="s">
         <v>499</v>
       </c>
-      <c r="J34" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" t="s">
-        <v>61</v>
-      </c>
-      <c r="L34" t="s">
-        <v>1</v>
-      </c>
-      <c r="M34" t="s">
-        <v>502</v>
-      </c>
       <c r="N34" t="s">
         <v>3</v>
       </c>
@@ -5418,92 +5421,92 @@
         <v>3</v>
       </c>
       <c r="P34" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="U34" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="V34" t="s">
         <v>5</v>
       </c>
       <c r="W34" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="35" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="D35" s="7">
-        <v>0</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="7" t="s">
+      <c r="J35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M35" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="N35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="J35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M35" s="7" t="s">
+      <c r="Q35" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="U35" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="N35" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="U35" s="7" t="s">
-        <v>513</v>
-      </c>
       <c r="V35" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W35" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="36" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D36" s="7">
         <v>2.5</v>
@@ -5512,60 +5515,60 @@
         <v>1630</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H36" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P36" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="Q36" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="U36" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="J36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="N36" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P36" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q36" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="U36" s="7" t="s">
-        <v>520</v>
-      </c>
       <c r="V36" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W36" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D37" s="7">
         <v>4</v>
@@ -5574,131 +5577,131 @@
         <v>5</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H37" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="N37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P37" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="Q37" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="U37" s="7" t="s">
         <v>525</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="N37" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O37" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P37" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q37" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="U37" s="7" t="s">
-        <v>528</v>
       </c>
       <c r="V37" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W37" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="38" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="I38" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="J38" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M38" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D38" s="7">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H38" s="7" t="s">
+      <c r="N38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="Q38" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="J38" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="L38" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M38" s="7" t="s">
+      <c r="R38" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="N38" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="7" t="s">
+      <c r="S38" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="Q38" s="7" t="s">
+      <c r="T38" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="R38" s="7" t="s">
+      <c r="U38" s="7" t="s">
         <v>462</v>
-      </c>
-      <c r="S38" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="T38" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="U38" s="7" t="s">
-        <v>465</v>
       </c>
       <c r="V38" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W38" s="7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D39" s="7">
         <v>5</v>
@@ -5713,63 +5716,63 @@
         <v>1</v>
       </c>
       <c r="H39" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P39" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="Q39" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="J39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M39" s="7" t="s">
+      <c r="R39" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="N39" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P39" s="7" t="s">
+      <c r="S39" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="Q39" s="7" t="s">
+      <c r="T39" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="R39" s="7" t="s">
+      <c r="U39" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="S39" s="7" t="s">
+      <c r="V39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W39" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="T39" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="U39" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="V39" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W39" s="7" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="40" spans="1:26" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D40" s="7">
         <v>3.4</v>
@@ -5784,63 +5787,63 @@
         <v>1</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I40" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P40" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="R40" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="J40" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M40" s="7" t="s">
+      <c r="S40" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="N40" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P40" s="9" t="s">
+      <c r="T40" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="Q40" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="R40" s="7" t="s">
+      <c r="U40" s="7" t="s">
         <v>487</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="T40" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="U40" s="7" t="s">
-        <v>490</v>
       </c>
       <c r="V40" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="41" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D41" s="7">
         <v>4</v>
@@ -5849,134 +5852,134 @@
         <v>823</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>1</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="I41" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="U41" s="7" t="s">
         <v>532</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M41" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="N41" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="Q41" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="U41" s="7" t="s">
-        <v>535</v>
       </c>
       <c r="V41" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W41" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="42" spans="1:26" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="C42" s="7" t="s">
+      <c r="J42" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M42" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="D42" s="7">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H42" s="7" t="s">
+      <c r="N42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="Q42" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="J42" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="L42" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M42" s="7" t="s">
+      <c r="R42" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="S42" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="N42" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="7" t="s">
+      <c r="T42" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="Q42" s="7" t="s">
+      <c r="U42" s="7" t="s">
         <v>544</v>
-      </c>
-      <c r="R42" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="S42" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="T42" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="U42" s="7" t="s">
-        <v>547</v>
       </c>
       <c r="V42" s="7" t="s">
         <v>5</v>
       </c>
       <c r="W42" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="Z42" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B43" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C43" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D43">
         <v>3.3</v>
@@ -5988,16 +5991,16 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H43" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="I43" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J43" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K43" t="s">
         <v>2</v>
@@ -6006,7 +6009,7 @@
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N43" t="s">
         <v>4</v>
@@ -6015,63 +6018,63 @@
         <v>4</v>
       </c>
       <c r="P43" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>555</v>
+      </c>
+      <c r="R43" t="s">
+        <v>556</v>
+      </c>
+      <c r="S43" t="s">
         <v>557</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="T43" t="s">
         <v>558</v>
       </c>
-      <c r="R43" t="s">
+      <c r="U43" t="s">
         <v>559</v>
-      </c>
-      <c r="S43" t="s">
-        <v>560</v>
-      </c>
-      <c r="T43" t="s">
-        <v>561</v>
-      </c>
-      <c r="U43" t="s">
-        <v>562</v>
       </c>
       <c r="V43" t="s">
         <v>5</v>
       </c>
       <c r="W43" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="Z43" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="44" spans="1:26" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="I44" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>681</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="J44" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="D44" s="7">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>569</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>2</v>
@@ -6080,125 +6083,125 @@
         <v>1</v>
       </c>
       <c r="M44" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="R44" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="9" t="s">
+      <c r="S44" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="Q44" s="7" t="s">
+      <c r="T44" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="R44" s="7" t="s">
+      <c r="U44" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="S44" s="7" t="s">
+      <c r="V44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W44" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="T44" s="7" t="s">
+      <c r="Z44" s="7" t="s">
         <v>575</v>
-      </c>
-      <c r="U44" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="V44" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W44" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="Z44" s="7" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="45" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>576</v>
+      </c>
+      <c r="B45" t="s">
+        <v>577</v>
+      </c>
+      <c r="C45" t="s">
+        <v>578</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
         <v>579</v>
       </c>
-      <c r="B45" t="s">
+      <c r="I45" t="s">
         <v>580</v>
       </c>
-      <c r="C45" t="s">
+      <c r="J45" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" t="s">
         <v>581</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45" t="s">
-        <v>0</v>
-      </c>
-      <c r="G45" t="s">
-        <v>1</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="L45" t="s">
+        <v>1</v>
+      </c>
+      <c r="M45" t="s">
         <v>582</v>
       </c>
-      <c r="I45" t="s">
+      <c r="N45" t="s">
         <v>583</v>
-      </c>
-      <c r="J45" t="s">
-        <v>73</v>
-      </c>
-      <c r="K45" t="s">
-        <v>584</v>
-      </c>
-      <c r="L45" t="s">
-        <v>1</v>
-      </c>
-      <c r="M45" t="s">
-        <v>585</v>
-      </c>
-      <c r="N45" t="s">
-        <v>586</v>
       </c>
       <c r="O45" t="s">
         <v>4</v>
       </c>
       <c r="P45" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>585</v>
+      </c>
+      <c r="R45" t="s">
+        <v>586</v>
+      </c>
+      <c r="S45" t="s">
         <v>587</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="T45" t="s">
         <v>588</v>
       </c>
-      <c r="R45" t="s">
+      <c r="U45" t="s">
         <v>589</v>
       </c>
-      <c r="S45" t="s">
+      <c r="V45" t="s">
         <v>590</v>
       </c>
-      <c r="T45" t="s">
+      <c r="W45" t="s">
         <v>591</v>
       </c>
-      <c r="U45" t="s">
+      <c r="Z45" t="s">
         <v>592</v>
-      </c>
-      <c r="V45" t="s">
-        <v>593</v>
-      </c>
-      <c r="W45" t="s">
-        <v>594</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="46" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D46" s="10">
         <v>3.7</v>
@@ -6213,63 +6216,63 @@
         <v>1</v>
       </c>
       <c r="H46" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="Q46" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="J46" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L46" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M46" s="10" t="s">
+      <c r="R46" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="N46" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="10" t="s">
+      <c r="S46" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="Q46" s="10" t="s">
+      <c r="T46" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="R46" s="10" t="s">
+      <c r="U46" s="10" t="s">
         <v>605</v>
-      </c>
-      <c r="S46" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="T46" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="U46" s="10" t="s">
-        <v>608</v>
       </c>
       <c r="V46" s="10" t="s">
         <v>5</v>
       </c>
       <c r="W46" s="10" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D47" s="10">
         <v>5</v>
@@ -6284,134 +6287,134 @@
         <v>1</v>
       </c>
       <c r="H47" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M47" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="N47" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="O47" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="K47" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M47" s="10" t="s">
+      <c r="Q47" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="N47" s="10" t="s">
+      <c r="R47" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="O47" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="P47" s="10" t="s">
+      <c r="S47" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="Q47" s="10" t="s">
+      <c r="T47" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="R47" s="10" t="s">
+      <c r="U47" s="10" t="s">
         <v>620</v>
-      </c>
-      <c r="S47" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="T47" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="U47" s="10" t="s">
-        <v>623</v>
       </c>
       <c r="V47" s="10" t="s">
         <v>5</v>
       </c>
       <c r="W47" s="10" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="48" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="D48" s="10">
+        <v>0</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="I48" s="10" t="s">
         <v>626</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="J48" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="D48" s="10">
-        <v>0</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H48" s="10" t="s">
+      <c r="K48" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M48" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="N48" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="J48" s="10" t="s">
+      <c r="Q48" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="K48" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="M48" s="10" t="s">
+      <c r="R48" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="N48" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="10" t="s">
+      <c r="S48" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="Q48" s="10" t="s">
+      <c r="T48" s="10" t="s">
         <v>633</v>
       </c>
-      <c r="R48" s="10" t="s">
+      <c r="U48" s="10" t="s">
         <v>634</v>
-      </c>
-      <c r="S48" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="T48" s="10" t="s">
-        <v>636</v>
-      </c>
-      <c r="U48" s="10" t="s">
-        <v>637</v>
       </c>
       <c r="V48" s="10" t="s">
         <v>5</v>
       </c>
       <c r="W48" s="10" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="49" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D49" s="10">
         <v>3.8</v>
@@ -6426,13 +6429,13 @@
         <v>1</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>2</v>
@@ -6441,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="N49" s="10" t="s">
         <v>4</v>
@@ -6450,60 +6453,60 @@
         <v>3</v>
       </c>
       <c r="P49" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="Q49" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="R49" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="S49" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="Q49" s="10" t="s">
+      <c r="T49" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="R49" s="10" t="s">
+      <c r="U49" s="10" t="s">
         <v>647</v>
-      </c>
-      <c r="S49" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="T49" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="U49" s="10" t="s">
-        <v>650</v>
       </c>
       <c r="V49" s="10" t="s">
         <v>5</v>
       </c>
       <c r="W49" s="10" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="50" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="D50" s="10">
+        <v>1</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H50" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="I50" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="D50" s="10">
-        <v>1</v>
-      </c>
-      <c r="E50" s="10">
-        <v>1</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>655</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>656</v>
-      </c>
       <c r="J50" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K50" s="10" t="s">
         <v>2</v>
@@ -6512,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="M50" s="10" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="N50" s="10" t="s">
         <v>3</v>
@@ -6521,39 +6524,39 @@
         <v>4</v>
       </c>
       <c r="P50" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="Q50" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="R50" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="S50" s="10" t="s">
         <v>658</v>
       </c>
-      <c r="Q50" s="10" t="s">
+      <c r="T50" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="R50" s="10" t="s">
+      <c r="U50" s="10" t="s">
         <v>660</v>
-      </c>
-      <c r="S50" s="10" t="s">
-        <v>661</v>
-      </c>
-      <c r="T50" s="10" t="s">
-        <v>662</v>
-      </c>
-      <c r="U50" s="10" t="s">
-        <v>663</v>
       </c>
       <c r="V50" s="10" t="s">
         <v>5</v>
       </c>
       <c r="W50" s="10" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="51" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D51" s="10">
         <v>5</v>
@@ -6568,52 +6571,52 @@
         <v>1</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="K51" s="10" t="s">
         <v>2</v>
       </c>
       <c r="L51" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="O51" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="M51" s="10" t="s">
+      <c r="P51" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="N51" s="10" t="s">
+      <c r="Q51" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="O51" s="10" t="s">
+      <c r="R51" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="P51" s="10" t="s">
+      <c r="S51" s="10" t="s">
         <v>674</v>
       </c>
-      <c r="Q51" s="10" t="s">
+      <c r="T51" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="R51" s="10" t="s">
+      <c r="U51" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="S51" s="10" t="s">
+      <c r="V51" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="W51" s="10" t="s">
         <v>677</v>
-      </c>
-      <c r="T51" s="10" t="s">
-        <v>678</v>
-      </c>
-      <c r="U51" s="10" t="s">
-        <v>679</v>
-      </c>
-      <c r="V51" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="W51" s="10" t="s">
-        <v>680</v>
       </c>
     </row>
   </sheetData>
